--- a/public/certificate_form.xlsx
+++ b/public/certificate_form.xlsx
@@ -1078,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.8333333333333" customWidth="1" min="1" max="4"/>
@@ -1098,6 +1098,30 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEBOSH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OSHA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
